--- a/tubes-compro/Data/files/atc_roster_output.xlsx
+++ b/tubes-compro/Data/files/atc_roster_output.xlsx
@@ -64,12 +64,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5E8D4"/>
+        <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D5E8D4"/>
       </patternFill>
     </fill>
     <fill>
@@ -79,7 +79,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -150,6 +150,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -790,70 +791,70 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>St2/C</t>
+          <t>Pt2/C</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
+          <t>Pt1/C</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
+          <t>Pt2/A</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>St1/C</t>
         </is>
@@ -865,75 +866,75 @@
       </c>
       <c r="T4" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="V4" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="Z4" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="AA4" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
+          <t>Pt2/A</t>
         </is>
       </c>
       <c r="AB4" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AC4" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AD4" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="AE4" s="7" t="inlineStr">
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="AD4" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
       <c r="AF4" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AG4" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AH4" s="7" t="inlineStr">
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="AG4" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
@@ -942,10 +943,10 @@
         <v>216</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AL4" s="3" t="n">
         <v>4</v>
@@ -975,152 +976,152 @@
           <t>TWR</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>IELP</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>IELP</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/A</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="V5" s="7" t="inlineStr">
+        <is>
+          <t>CUTI</t>
+        </is>
+      </c>
+      <c r="W5" s="7" t="inlineStr">
+        <is>
+          <t>CUTI</t>
+        </is>
+      </c>
+      <c r="X5" s="7" t="inlineStr">
+        <is>
+          <t>CUTI</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="Z5" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AA5" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AB5" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AC5" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AD5" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AE5" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>IELP</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>IELP</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="V5" s="5" t="inlineStr">
-        <is>
-          <t>CUTI</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="inlineStr">
-        <is>
-          <t>CUTI</t>
-        </is>
-      </c>
-      <c r="X5" s="5" t="inlineStr">
-        <is>
-          <t>CUTI</t>
-        </is>
-      </c>
-      <c r="Y5" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AB5" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AE5" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AF5" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AG5" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AH5" s="4" t="inlineStr">
+      <c r="AG5" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AH5" s="5" t="inlineStr">
         <is>
           <t>St2/A</t>
         </is>
@@ -1129,10 +1130,10 @@
         <v>198</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL5" s="3" t="n">
         <v>3</v>
@@ -1162,141 +1163,141 @@
           <t>TWR</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="U6" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="S6" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="T6" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="V6" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="AA6" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AB6" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="AD6" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
       </c>
-      <c r="X6" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="Y6" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/A</t>
-        </is>
-      </c>
-      <c r="Z6" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AB6" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AD6" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AE6" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
       <c r="AF6" s="9" t="inlineStr">
         <is>
           <t>DIKLAT</t>
@@ -1307,22 +1308,22 @@
           <t>DIKLAT</t>
         </is>
       </c>
-      <c r="AH6" s="4" t="inlineStr">
+      <c r="AH6" s="5" t="inlineStr">
         <is>
           <t>St1/A</t>
         </is>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM6" s="3" t="n">
         <v>2</v>
@@ -1349,27 +1350,27 @@
           <t>TWR</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>St1/A</t>
         </is>
@@ -1384,129 +1385,129 @@
           <t>SAKIT</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="R7" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="S7" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="T7" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
+          <t>Pt1/A</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="W7" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
         </is>
       </c>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
+          <t>Pt2/A</t>
         </is>
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
+          <t>Pt1/A</t>
         </is>
       </c>
       <c r="Z7" s="4" t="inlineStr">
         <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AB7" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AD7" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AE7" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AF7" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AG7" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="AA7" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AB7" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AC7" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AD7" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AE7" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AF7" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AG7" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="AH7" s="4" t="inlineStr">
         <is>
-          <t>St2/C</t>
+          <t>Pt2/C</t>
         </is>
       </c>
       <c r="AI7" s="3" t="n">
         <v>207</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AL7" s="3" t="n">
         <v>5</v>
@@ -1538,165 +1539,165 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
+          <t>Pt1/A</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="R8" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="S8" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="V8" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
+      <c r="Y8" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="Z8" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AA8" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AB8" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AC8" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="W8" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="Y8" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="Z8" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="AA8" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AB8" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AD8" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AE8" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AF8" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AG8" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AH8" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="AE8" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AF8" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AG8" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AH8" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
         </is>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM8" s="3" t="n">
         <v>3</v>
@@ -1723,92 +1724,92 @@
           <t>TWR</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
+          <t>Pt2/A</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
         </is>
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="inlineStr">
         <is>
           <t>St2/A</t>
         </is>
@@ -1818,72 +1819,72 @@
           <t>OFF</t>
         </is>
       </c>
-      <c r="X9" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="Y9" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="Z9" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AB9" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AC9" s="5" t="inlineStr">
+      <c r="X9" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="Y9" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="Z9" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AA9" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AB9" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AC9" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="AD9" s="5" t="inlineStr">
+      <c r="AD9" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="AE9" s="5" t="inlineStr">
+      <c r="AE9" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="AF9" s="5" t="inlineStr">
+      <c r="AF9" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="AG9" s="7" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="AH9" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/A</t>
+      <c r="AH9" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
         </is>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM9" s="3" t="n">
         <v>4</v>
@@ -1910,132 +1911,132 @@
           <t>TWR</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="X10" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="R10" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="S10" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="V10" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AA10" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AB10" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AD10" s="4" t="inlineStr">
+      <c r="Z10" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AA10" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AB10" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AC10" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AD10" s="5" t="inlineStr">
         <is>
           <t>St1/A</t>
         </is>
@@ -2047,30 +2048,30 @@
       </c>
       <c r="AF10" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AG10" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="AG10" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="AH10" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
+          <t>Pt1/A</t>
         </is>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM10" s="3" t="n">
         <v>2</v>
@@ -2097,154 +2098,154 @@
           <t>TWR</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="T11" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="R11" s="7" t="inlineStr">
+      <c r="W11" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="X11" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="Y11" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="Z11" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AA11" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="AC11" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AD11" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AE11" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AF11" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AG11" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="AH11" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="S11" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="U11" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="Y11" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="Z11" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="AA11" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="AB11" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AF11" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AG11" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="AH11" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
         </is>
       </c>
       <c r="AI11" s="3" t="n">
@@ -2284,167 +2285,167 @@
           <t>TWR</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>DIKLAT</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>DIKLAT</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="W12" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="X12" s="9" t="inlineStr">
         <is>
           <t>DIKLAT</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="Y12" s="9" t="inlineStr">
         <is>
           <t>DIKLAT</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="Z12" s="9" t="inlineStr">
+        <is>
+          <t>DIKLAT</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="AC12" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AD12" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AE12" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AF12" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AG12" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AH12" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/A</t>
-        </is>
-      </c>
-      <c r="T12" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="U12" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="W12" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/A</t>
-        </is>
-      </c>
-      <c r="X12" s="9" t="inlineStr">
-        <is>
-          <t>DIKLAT</t>
-        </is>
-      </c>
-      <c r="Y12" s="9" t="inlineStr">
-        <is>
-          <t>DIKLAT</t>
-        </is>
-      </c>
-      <c r="Z12" s="9" t="inlineStr">
-        <is>
-          <t>DIKLAT</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AB12" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AF12" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AG12" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AH12" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
       <c r="AI12" s="3" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="AJ12" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM12" s="3" t="n">
         <v>5</v>
@@ -2478,110 +2479,110 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
+          <t>Pt2/A</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="R13" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="S13" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="X13" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Y13" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="Z13" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AA13" s="4" t="inlineStr">
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="Z13" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AA13" s="5" t="inlineStr">
         <is>
           <t>St1/A</t>
         </is>
@@ -2598,40 +2599,40 @@
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AE13" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AF13" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AG13" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AH13" s="4" t="inlineStr">
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="AE13" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AF13" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AG13" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AH13" s="5" t="inlineStr">
         <is>
           <t>St2/A</t>
         </is>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AM13" s="3" t="n">
         <v>4</v>
@@ -2658,164 +2659,164 @@
           <t>APP</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>DIKLAT</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>DIKLAT</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>DIKLAT</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>DIKLAT</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>DIKLAT</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>DIKLAT</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>DIKLAT</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>DIKLAT</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>DIKLAT</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>DIKLAT</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/A</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="X14" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="Y14" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="Z14" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="AC14" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AD14" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AE14" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AF14" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AG14" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AH14" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="R14" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="Z14" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AA14" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="AB14" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="AC14" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AF14" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AG14" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AH14" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
         </is>
       </c>
       <c r="AI14" s="3" t="n">
         <v>180</v>
       </c>
       <c r="AJ14" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL14" s="3" t="n">
         <v>5</v>
@@ -2845,149 +2846,149 @@
           <t>APP</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>DIKLAT</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>DIKLAT</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>DIKLAT</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>DIKLAT</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>DIKLAT</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>DIKLAT</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>DIKLAT</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>DIKLAT</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>DIKLAT</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>DIKLAT</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="X15" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="Y15" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="R15" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="T15" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="Z15" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AA15" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="AB15" s="7" t="inlineStr">
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="AA15" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AB15" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="AC15" s="7" t="inlineStr">
+      <c r="AC15" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="AD15" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AE15" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AF15" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AG15" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="AD15" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AE15" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AF15" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AG15" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
         </is>
       </c>
       <c r="AH15" s="6" t="inlineStr">
@@ -2999,10 +3000,10 @@
         <v>189</v>
       </c>
       <c r="AJ15" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AL15" s="3" t="n">
         <v>4</v>
@@ -3032,102 +3033,102 @@
           <t>APP</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="R16" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="T16" s="7" t="inlineStr">
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="X16" s="4" t="inlineStr">
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="X16" s="5" t="inlineStr">
         <is>
           <t>St1/A</t>
         </is>
@@ -3137,7 +3138,7 @@
           <t>OFF</t>
         </is>
       </c>
-      <c r="Z16" s="4" t="inlineStr">
+      <c r="Z16" s="5" t="inlineStr">
         <is>
           <t>St1/C</t>
         </is>
@@ -3147,49 +3148,49 @@
           <t>OFF</t>
         </is>
       </c>
-      <c r="AB16" s="7" t="inlineStr">
+      <c r="AB16" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="AC16" s="5" t="inlineStr">
+      <c r="AC16" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="AD16" s="5" t="inlineStr">
+      <c r="AD16" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="AE16" s="5" t="inlineStr">
+      <c r="AE16" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="AF16" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="AG16" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="AH16" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
+      <c r="AF16" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AG16" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AH16" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
         </is>
       </c>
       <c r="AI16" s="3" t="n">
         <v>198</v>
       </c>
       <c r="AJ16" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AL16" s="3" t="n">
         <v>5</v>
@@ -3219,39 +3220,39 @@
           <t>APP</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
+          <t>Pt1/A</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>St2/C</t>
+          <t>Pt2/C</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -3269,117 +3270,117 @@
           <t>DIKLAT</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="Q17" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="R17" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="S17" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="inlineStr">
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="X17" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="Y17" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="Z17" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="W17" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="Y17" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="Z17" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AA17" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AB17" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AC17" s="7" t="inlineStr">
+      <c r="AA17" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AB17" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AC17" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AD17" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AE17" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AF17" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="AD17" s="7" t="inlineStr">
+      <c r="AH17" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="AE17" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="AF17" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="AG17" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AH17" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
       <c r="AI17" s="3" t="n">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="AJ17" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AM17" s="3" t="n">
         <v>3</v>
@@ -3406,167 +3407,167 @@
           <t>APP</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>St2/C</t>
+          <t>Pt2/C</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
+          <t>Pt1/C</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="W18" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="X18" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="Y18" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="Z18" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="AA18" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AB18" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AC18" s="5" t="inlineStr">
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="U18" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="X18" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="Y18" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="Z18" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AA18" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AB18" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AC18" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="AD18" s="5" t="inlineStr">
+      <c r="AD18" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="AE18" s="7" t="inlineStr">
+      <c r="AE18" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
       </c>
       <c r="AF18" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AG18" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AH18" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="AG18" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AH18" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
         </is>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="AJ18" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM18" s="3" t="n">
         <v>2</v>
@@ -3578,12 +3579,12 @@
           <t>A06</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Prasetyo Adi</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
@@ -3593,167 +3594,167 @@
           <t>APP</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
+          <t>Pt2/A</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
+          <t>Pt1/A</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="inlineStr">
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="R19" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="S19" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="T19" s="7" t="inlineStr">
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="U19" s="7" t="inlineStr">
+      <c r="U19" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="V19" s="7" t="inlineStr">
+      <c r="V19" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
       </c>
-      <c r="W19" s="7" t="inlineStr">
+      <c r="W19" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="X19" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="Y19" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="Z19" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="AA19" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="X19" s="7" t="inlineStr">
+      <c r="AB19" s="7" t="inlineStr">
+        <is>
+          <t>CUTI</t>
+        </is>
+      </c>
+      <c r="AC19" s="7" t="inlineStr">
+        <is>
+          <t>CUTI</t>
+        </is>
+      </c>
+      <c r="AD19" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="AE19" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="AF19" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="Y19" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="Z19" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AA19" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AB19" s="5" t="inlineStr">
-        <is>
-          <t>CUTI</t>
-        </is>
-      </c>
-      <c r="AC19" s="5" t="inlineStr">
-        <is>
-          <t>CUTI</t>
-        </is>
-      </c>
-      <c r="AD19" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="AE19" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="AF19" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/A</t>
-        </is>
-      </c>
       <c r="AG19" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AH19" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="AH19" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="AJ19" s="3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM19" s="3" t="n">
         <v>4</v>
@@ -3780,19 +3781,19 @@
           <t>APP</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
+          <t>Pt1/C</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
+          <t>Pt2/A</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -3800,22 +3801,22 @@
           <t>OFF</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>St1/A</t>
         </is>
@@ -3827,12 +3828,12 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="O20" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
@@ -3840,89 +3841,89 @@
           <t>OFF</t>
         </is>
       </c>
-      <c r="Q20" s="7" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="T20" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="X20" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="Y20" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="Z20" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AA20" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AB20" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="AC20" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
       </c>
-      <c r="R20" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="S20" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="T20" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="U20" s="7" t="inlineStr">
+      <c r="AD20" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="AE20" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="AF20" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="V20" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="W20" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/A</t>
-        </is>
-      </c>
-      <c r="X20" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="Y20" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="Z20" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AB20" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="AC20" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AD20" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AE20" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AF20" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AG20" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
         </is>
       </c>
       <c r="AH20" s="6" t="inlineStr">
@@ -3934,10 +3935,10 @@
         <v>207</v>
       </c>
       <c r="AJ20" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AL20" s="3" t="n">
         <v>6</v>
@@ -3969,32 +3970,32 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
+          <t>Pt1/C</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
+          <t>Pt2/A</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
+          <t>Pt1/A</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>St2/C</t>
+          <t>Pt2/C</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
+          <t>Pt1/C</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
+          <t>Pt2/A</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -4002,132 +4003,132 @@
           <t>OFF</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="N21" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="O21" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>SAKIT</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>SAKIT</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>SAKIT</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="X21" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
       </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
+      <c r="Y21" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="Z21" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AA21" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AB21" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AC21" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AD21" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>SAKIT</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>SAKIT</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>SAKIT</t>
-        </is>
-      </c>
-      <c r="W21" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="X21" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="Y21" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="Z21" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AA21" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AB21" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AC21" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AD21" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AE21" s="5" t="inlineStr">
+      <c r="AE21" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="AF21" s="5" t="inlineStr">
+      <c r="AF21" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="AG21" s="5" t="inlineStr">
+      <c r="AG21" s="7" t="inlineStr">
         <is>
           <t>CUTI</t>
         </is>
       </c>
-      <c r="AH21" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
+      <c r="AH21" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="AJ21" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AL21" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM21" s="3" t="n">
         <v>6</v>
@@ -4154,167 +4155,167 @@
           <t>GMC</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="R22" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/A</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/A</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="O22" s="7" t="inlineStr">
+      <c r="S22" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>CUTI</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
+        <is>
+          <t>CUTI</t>
+        </is>
+      </c>
+      <c r="W22" s="7" t="inlineStr">
+        <is>
+          <t>CUTI</t>
+        </is>
+      </c>
+      <c r="X22" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="Y22" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="Z22" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AA22" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AB22" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AC22" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AD22" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AE22" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
       </c>
-      <c r="P22" s="7" t="inlineStr">
+      <c r="AF22" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/A</t>
-        </is>
-      </c>
-      <c r="R22" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="T22" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="U22" s="5" t="inlineStr">
-        <is>
-          <t>CUTI</t>
-        </is>
-      </c>
-      <c r="V22" s="5" t="inlineStr">
-        <is>
-          <t>CUTI</t>
-        </is>
-      </c>
-      <c r="W22" s="5" t="inlineStr">
-        <is>
-          <t>CUTI</t>
-        </is>
-      </c>
-      <c r="X22" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="Y22" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="Z22" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AA22" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AB22" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AC22" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AD22" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AE22" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AF22" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AG22" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AH22" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="AG22" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AH22" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
         </is>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="AJ22" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM22" s="3" t="n">
         <v>3</v>
@@ -4341,167 +4342,167 @@
           <t>GMC</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="T23" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="U23" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="R23" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="V23" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="T23" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="V23" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="W23" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
       <c r="X23" s="6" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="Y23" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="Z23" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AA23" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AB23" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AC23" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AD23" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AE23" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AF23" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AG23" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AH23" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
+      <c r="Y23" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="Z23" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AA23" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AB23" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AC23" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AD23" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AE23" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AF23" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AG23" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AH23" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
         </is>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="AJ23" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>17</v>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM23" s="3" t="n">
         <v>0</v>
@@ -4528,92 +4529,92 @@
           <t>GMC</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>CUTI</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>CUTI</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>CUTI</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>CUTI</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>CUTI</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>CUTI</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
+          <t>Pt1/C</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="P24" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="S24" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="U24" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="inlineStr">
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="inlineStr">
         <is>
           <t>St1/C</t>
         </is>
@@ -4628,7 +4629,7 @@
           <t>SAKIT</t>
         </is>
       </c>
-      <c r="Y24" s="7" t="inlineStr">
+      <c r="Y24" s="4" t="inlineStr">
         <is>
           <t>Pt2/C</t>
         </is>
@@ -4638,42 +4639,42 @@
           <t>OFF</t>
         </is>
       </c>
-      <c r="AA24" s="7" t="inlineStr">
+      <c r="AA24" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AB24" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AC24" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="AD24" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="AE24" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="AB24" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AC24" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AD24" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="AE24" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/A</t>
-        </is>
-      </c>
       <c r="AF24" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AG24" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="AH24" s="4" t="inlineStr">
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="AG24" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AH24" s="5" t="inlineStr">
         <is>
           <t>St1/C</t>
         </is>
@@ -4682,10 +4683,10 @@
         <v>180</v>
       </c>
       <c r="AJ24" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AL24" s="3" t="n">
         <v>5</v>
@@ -4715,114 +4716,114 @@
           <t>GMC</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="U25" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="V25" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="O25" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="P25" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="R25" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="S25" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="T25" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="U25" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="V25" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="W25" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="X25" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="Y25" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="Z25" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="X25" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="Y25" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="Z25" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
         </is>
       </c>
       <c r="AA25" s="9" t="inlineStr">
@@ -4835,47 +4836,47 @@
           <t>DIKLAT</t>
         </is>
       </c>
-      <c r="AC25" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
+      <c r="AC25" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="AD25" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AE25" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AF25" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AG25" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="AH25" s="7" t="inlineStr">
-        <is>
           <t>Pt2/A</t>
         </is>
       </c>
+      <c r="AE25" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AF25" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AG25" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="AH25" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
       <c r="AI25" s="3" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="AJ25" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM25" s="3" t="n">
         <v>2</v>
@@ -4902,167 +4903,167 @@
           <t>GMC</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="R26" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="U26" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/A</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="X26" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr">
+      <c r="Y26" s="4" t="inlineStr">
         <is>
           <t>Pt2/A</t>
         </is>
       </c>
-      <c r="N26" s="7" t="inlineStr">
+      <c r="Z26" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AA26" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="AB26" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AC26" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="AD26" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AE26" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AF26" s="4" t="inlineStr">
+        <is>
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="AG26" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="AH26" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="O26" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="P26" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="R26" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="S26" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="V26" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="W26" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/C</t>
-        </is>
-      </c>
-      <c r="X26" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="Y26" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/A</t>
-        </is>
-      </c>
-      <c r="Z26" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/A</t>
-        </is>
-      </c>
-      <c r="AA26" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AB26" s="7" t="inlineStr">
-        <is>
-          <t>Pt1/C</t>
-        </is>
-      </c>
-      <c r="AC26" s="7" t="inlineStr">
-        <is>
-          <t>Pt2/A</t>
-        </is>
-      </c>
-      <c r="AD26" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AE26" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AF26" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AG26" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AH26" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
       <c r="AI26" s="3" t="n">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="AJ26" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AL26" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM26" s="3" t="n">
         <v>0</v>
@@ -5089,47 +5090,47 @@
           <t>GMC</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/C</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>St1/A</t>
         </is>
@@ -5139,17 +5140,17 @@
           <t>OFF</t>
         </is>
       </c>
-      <c r="O27" s="7" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>Pt1/C</t>
         </is>
       </c>
-      <c r="P27" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
+      <c r="P27" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="Q27" s="5" t="inlineStr">
         <is>
           <t>St1/A</t>
         </is>
@@ -5159,97 +5160,97 @@
           <t>OFF</t>
         </is>
       </c>
-      <c r="S27" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="T27" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="U27" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="V27" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="W27" s="4" t="inlineStr">
-        <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="X27" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
+          <t>St1/C</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="inlineStr">
+        <is>
+          <t>St2/C</t>
+        </is>
+      </c>
+      <c r="W27" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="X27" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
         </is>
       </c>
       <c r="Y27" s="4" t="inlineStr">
         <is>
-          <t>St1/A</t>
+          <t>Pt1/A</t>
         </is>
       </c>
       <c r="Z27" s="4" t="inlineStr">
         <is>
-          <t>St2/C</t>
+          <t>Pt2/C</t>
         </is>
       </c>
       <c r="AA27" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AB27" s="6" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="AC27" s="7" t="inlineStr">
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="AB27" s="4" t="inlineStr">
+        <is>
+          <t>Pt2/A</t>
+        </is>
+      </c>
+      <c r="AC27" s="4" t="inlineStr">
         <is>
           <t>Pt1/A</t>
         </is>
       </c>
-      <c r="AD27" s="4" t="inlineStr">
-        <is>
-          <t>St2/C</t>
+      <c r="AD27" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
         </is>
       </c>
       <c r="AE27" s="4" t="inlineStr">
         <is>
-          <t>St1/C</t>
-        </is>
-      </c>
-      <c r="AF27" s="4" t="inlineStr">
-        <is>
-          <t>St2/A</t>
-        </is>
-      </c>
-      <c r="AG27" s="4" t="inlineStr">
-        <is>
-          <t>St1/A</t>
-        </is>
-      </c>
-      <c r="AH27" s="4" t="inlineStr">
+          <t>Pt1/C</t>
+        </is>
+      </c>
+      <c r="AF27" s="5" t="inlineStr">
+        <is>
+          <t>St2/A</t>
+        </is>
+      </c>
+      <c r="AG27" s="5" t="inlineStr">
+        <is>
+          <t>St1/A</t>
+        </is>
+      </c>
+      <c r="AH27" s="5" t="inlineStr">
         <is>
           <t>St2/C</t>
         </is>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="AJ27" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AL27" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM27" s="3" t="n">
         <v>0</v>
@@ -5269,7 +5270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -5312,7 +5313,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6">
@@ -5322,13 +5323,104 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Detail:</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>[LUNAK-S3] hari-2: distribusi timpang Pagi=9 vs Siang=12 (selisih 3, maks 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>[LUNAK-S3] hari-3: distribusi timpang Pagi=8 vs Siang=13 (selisih 5, maks 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>[LUNAK-S3] hari-4: distribusi timpang Pagi=7 vs Siang=11 (selisih 4, maks 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>[LUNAK-S3] hari-6: distribusi timpang Pagi=7 vs Siang=11 (selisih 4, maks 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>[LUNAK-S3] hari-9: distribusi timpang Pagi=8 vs Siang=11 (selisih 3, maks 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>[LUNAK-S3] hari-12: distribusi timpang Pagi=7 vs Siang=11 (selisih 4, maks 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>[LUNAK-S3] hari-13: distribusi timpang Pagi=7 vs Siang=12 (selisih 5, maks 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>[LUNAK-S3] hari-16: distribusi timpang Pagi=8 vs Siang=11 (selisih 3, maks 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>[LUNAK-S3] hari-18: distribusi timpang Pagi=8 vs Siang=11 (selisih 3, maks 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>[LUNAK-S3] hari-22: distribusi timpang Pagi=6 vs Siang=14 (selisih 8, maks 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>[LUNAK-S3] hari-23: distribusi timpang Pagi=5 vs Siang=13 (selisih 8, maks 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>[LUNAK-S3] hari-29: distribusi timpang Pagi=6 vs Siang=10 (selisih 4, maks 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>[LUNAK-S3] hari-30: distribusi timpang Pagi=8 vs Siang=12 (selisih 4, maks 2)</t>
         </is>
       </c>
     </row>
@@ -5357,42 +5449,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>EMP_ID</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>NAMA</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>TOTAL_JAM</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>JML_S1</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>JML_S2</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>JML_OFF</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>JML_CUTI</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>PERSENTASE_KERJA</t>
         </is>
@@ -5427,7 +5519,7 @@
         <f>Roster!AM4</f>
         <v/>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="14">
         <f>(D2+E2)/30</f>
         <v/>
       </c>
@@ -5461,7 +5553,7 @@
         <f>Roster!AM5</f>
         <v/>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="14">
         <f>(D3+E3)/30</f>
         <v/>
       </c>
@@ -5495,7 +5587,7 @@
         <f>Roster!AM6</f>
         <v/>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="14">
         <f>(D4+E4)/30</f>
         <v/>
       </c>
@@ -5529,7 +5621,7 @@
         <f>Roster!AM7</f>
         <v/>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="14">
         <f>(D5+E5)/30</f>
         <v/>
       </c>
@@ -5563,7 +5655,7 @@
         <f>Roster!AM8</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <f>(D6+E6)/30</f>
         <v/>
       </c>
@@ -5597,7 +5689,7 @@
         <f>Roster!AM9</f>
         <v/>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="14">
         <f>(D7+E7)/30</f>
         <v/>
       </c>
@@ -5631,7 +5723,7 @@
         <f>Roster!AM10</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <f>(D8+E8)/30</f>
         <v/>
       </c>
@@ -5665,7 +5757,7 @@
         <f>Roster!AM11</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="14">
         <f>(D9+E9)/30</f>
         <v/>
       </c>
@@ -5699,7 +5791,7 @@
         <f>Roster!AM12</f>
         <v/>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="14">
         <f>(D10+E10)/30</f>
         <v/>
       </c>
@@ -5733,7 +5825,7 @@
         <f>Roster!AM13</f>
         <v/>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="14">
         <f>(D11+E11)/30</f>
         <v/>
       </c>
@@ -5767,7 +5859,7 @@
         <f>Roster!AM14</f>
         <v/>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="14">
         <f>(D12+E12)/30</f>
         <v/>
       </c>
@@ -5801,7 +5893,7 @@
         <f>Roster!AM15</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="14">
         <f>(D13+E13)/30</f>
         <v/>
       </c>
@@ -5835,7 +5927,7 @@
         <f>Roster!AM16</f>
         <v/>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="14">
         <f>(D14+E14)/30</f>
         <v/>
       </c>
@@ -5869,7 +5961,7 @@
         <f>Roster!AM17</f>
         <v/>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="14">
         <f>(D15+E15)/30</f>
         <v/>
       </c>
@@ -5903,7 +5995,7 @@
         <f>Roster!AM18</f>
         <v/>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="14">
         <f>(D16+E16)/30</f>
         <v/>
       </c>
@@ -5937,7 +6029,7 @@
         <f>Roster!AM19</f>
         <v/>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="14">
         <f>(D17+E17)/30</f>
         <v/>
       </c>
@@ -5971,7 +6063,7 @@
         <f>Roster!AM20</f>
         <v/>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="14">
         <f>(D18+E18)/30</f>
         <v/>
       </c>
@@ -6005,7 +6097,7 @@
         <f>Roster!AM21</f>
         <v/>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="14">
         <f>(D19+E19)/30</f>
         <v/>
       </c>
@@ -6039,7 +6131,7 @@
         <f>Roster!AM22</f>
         <v/>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="14">
         <f>(D20+E20)/30</f>
         <v/>
       </c>
@@ -6073,7 +6165,7 @@
         <f>Roster!AM23</f>
         <v/>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="14">
         <f>(D21+E21)/30</f>
         <v/>
       </c>
@@ -6107,7 +6199,7 @@
         <f>Roster!AM24</f>
         <v/>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="14">
         <f>(D22+E22)/30</f>
         <v/>
       </c>
@@ -6141,7 +6233,7 @@
         <f>Roster!AM25</f>
         <v/>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="14">
         <f>(D23+E23)/30</f>
         <v/>
       </c>
@@ -6175,7 +6267,7 @@
         <f>Roster!AM26</f>
         <v/>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="14">
         <f>(D24+E24)/30</f>
         <v/>
       </c>
@@ -6209,7 +6301,7 @@
         <f>Roster!AM27</f>
         <v/>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="14">
         <f>(D25+E25)/30</f>
         <v/>
       </c>
